--- a/public/coffee/special.xlsx
+++ b/public/coffee/special.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elizaveta/Desktop/projects/sage/GkirillS.github.io/public/coffee/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E5A0FE-D81D-DA43-99A0-846FB58E30A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23862F14-07CE-9244-B011-01EABB18CE8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2480" yWindow="600" windowWidth="21260" windowHeight="16260" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2480" yWindow="600" windowWidth="21260" windowHeight="16260" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Maslenitsa" sheetId="3" r:id="rId1"/>
+    <sheet name="Special" sheetId="3" r:id="rId1"/>
     <sheet name="Seasonal Drinks" sheetId="1" r:id="rId2"/>
     <sheet name="catalogs" sheetId="2" r:id="rId3"/>
   </sheets>
@@ -210,12 +210,6 @@
     <t>Cезонные  напитки</t>
   </si>
   <si>
-    <t>Масленица</t>
-  </si>
-  <si>
-    <t>Maslenitsa</t>
-  </si>
-  <si>
     <t>Блин чизбургер</t>
   </si>
   <si>
@@ -241,6 +235,12 @@
   </si>
   <si>
     <t>ბლინები შესქელებული რძით და ბანანით</t>
+  </si>
+  <si>
+    <t>Спешл</t>
+  </si>
+  <si>
+    <t>Special</t>
   </si>
 </sst>
 </file>
@@ -789,13 +789,13 @@
     </row>
     <row r="2" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9">
@@ -815,13 +815,13 @@
     </row>
     <row r="3" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9">
@@ -841,13 +841,13 @@
     </row>
     <row r="4" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2">
@@ -16314,13 +16314,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
